--- a/touken_mst.xlsx
+++ b/touken_mst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\study\touken\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F105B6-A325-4A1E-9310-B526C57BE0E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F39D4EB-CFAB-4A07-947A-6F908D5C8431}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17556" windowHeight="7812" firstSheet="2" activeTab="6" xr2:uid="{5529400E-6EAE-4C1C-AD76-7C1ABC364E04}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6643" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6698" uniqueCount="744">
   <si>
     <t>童子切安綱 剥落</t>
     <rPh sb="0" eb="5">
@@ -5743,6 +5743,46 @@
   </si>
   <si>
     <t>parse</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1h30m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2h20m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1h25m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2h30m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3h00m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3h10m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4h00m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3h50m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3h20m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>??h??m</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -62230,7 +62270,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DAE05A-0EEE-4271-AA81-CE5AE56E1B0A}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.796875" style="2"/>
@@ -62239,15 +62279,18 @@
     <col min="7" max="16384" width="8.796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>159</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C2,
@@ -62269,8 +62312,11 @@
       <c r="F2" s="8">
         <v>5.8000000000000003E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G2" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C3,
@@ -62292,8 +62338,11 @@
       <c r="F3" s="8">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G3" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C4,
@@ -62315,8 +62364,11 @@
       <c r="F4" s="8">
         <v>5.1999999999999998E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G4" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C5,
@@ -62338,8 +62390,11 @@
       <c r="F5" s="8">
         <v>4.5999999999999999E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G5" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C6,
@@ -62361,8 +62416,11 @@
       <c r="F6" s="8">
         <v>6.3E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G6" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C7,
@@ -62384,8 +62442,11 @@
       <c r="F7" s="8">
         <v>5.2999999999999999E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G7" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C8,
@@ -62407,8 +62468,11 @@
       <c r="F8" s="8">
         <v>5.2999999999999999E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G8" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C9,
@@ -62430,8 +62494,11 @@
       <c r="F9" s="8">
         <v>6.5000000000000002E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G9" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C10,
@@ -62453,8 +62520,11 @@
       <c r="F10" s="8">
         <v>5.3999999999999999E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G10" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C11,
@@ -62476,8 +62546,11 @@
       <c r="F11" s="8">
         <v>5.5E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G11" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C12,
@@ -62499,8 +62572,11 @@
       <c r="F12" s="8">
         <v>5.8000000000000003E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G12" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C13,
@@ -62522,8 +62598,11 @@
       <c r="F13" s="8">
         <v>1.0999999999999999E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G13" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C14,
@@ -62545,8 +62624,11 @@
       <c r="F14" s="8">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G14" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C15,
@@ -62568,8 +62650,11 @@
       <c r="F15" s="8">
         <v>1.0999999999999999E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G15" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C16,
@@ -62591,8 +62676,11 @@
       <c r="F16" s="8">
         <v>5.7000000000000002E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G16" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C17,
@@ -62617,8 +62705,11 @@
       <c r="F17" s="8">
         <v>1.67E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G17" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C18,
@@ -62643,8 +62734,11 @@
       <c r="F18" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G18" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C19,
@@ -62669,8 +62763,11 @@
       <c r="F19" s="8">
         <v>9.1000000000000004E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G19" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C20,
@@ -62695,8 +62792,11 @@
       <c r="F20" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G20" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C21,
@@ -62721,8 +62821,11 @@
       <c r="F21" s="8">
         <v>1.21E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G21" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C22,
@@ -62747,8 +62850,11 @@
       <c r="F22" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G22" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C23,
@@ -62773,8 +62879,11 @@
       <c r="F23" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G23" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C24,
@@ -62799,8 +62908,11 @@
       <c r="F24" s="8">
         <v>9.1000000000000004E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G24" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C25,
@@ -62825,8 +62937,11 @@
       <c r="F25" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G25" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C26,
@@ -62851,8 +62966,11 @@
       <c r="F26" s="8">
         <v>3.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G26" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C27,
@@ -62877,8 +62995,11 @@
       <c r="F27" s="8">
         <v>3.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G27" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C28,
@@ -62903,8 +63024,11 @@
       <c r="F28" s="8">
         <v>3.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G28" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C29,
@@ -62929,8 +63053,11 @@
       <c r="F29" s="8">
         <v>7.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G29" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C30,
@@ -62955,8 +63082,11 @@
       <c r="F30" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G30" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C31,
@@ -62981,8 +63111,11 @@
       <c r="F31" s="8">
         <v>6.1000000000000004E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G31" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C32,
@@ -63007,8 +63140,11 @@
       <c r="F32" s="8">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G32" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C33,
@@ -63033,8 +63169,11 @@
       <c r="F33" s="8">
         <v>8.0000000000000004E-4</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G33" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C34,
@@ -63059,8 +63198,11 @@
       <c r="F34" s="8">
         <v>7.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G34" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C35,
@@ -63085,8 +63227,11 @@
       <c r="F35" s="8">
         <v>1.5E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G35" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C36,
@@ -63111,8 +63256,11 @@
       <c r="F36" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G36" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C37,
@@ -63137,8 +63285,11 @@
       <c r="F37" s="8">
         <v>7.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G37" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C38,
@@ -63160,8 +63311,11 @@
       <c r="F38" s="8">
         <v>1.7000000000000001E-2</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G38" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C39,
@@ -63186,8 +63340,11 @@
       <c r="F39" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G39" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C40,
@@ -63212,8 +63369,11 @@
       <c r="F40" s="8">
         <v>8.0000000000000002E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G40" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C41,
@@ -63238,8 +63398,11 @@
       <c r="F41" s="8">
         <v>1.7999999999999999E-2</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G41" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C42,
@@ -63261,8 +63424,11 @@
       <c r="F42" s="8">
         <v>2.1000000000000001E-2</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G42" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C43,
@@ -63287,8 +63453,11 @@
       <c r="F43" s="8">
         <v>8.0000000000000002E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G43" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C44,
@@ -63313,8 +63482,11 @@
       <c r="F44" s="8">
         <v>8.9999999999999993E-3</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G44" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C45,
@@ -63336,8 +63508,11 @@
       <c r="F45" s="8">
         <v>2.4E-2</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G45" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C46,
@@ -63362,8 +63537,11 @@
       <c r="F46" s="8">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G46" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C47,
@@ -63388,8 +63566,11 @@
       <c r="F47" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G47" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C48,
@@ -63414,8 +63595,11 @@
       <c r="F48" s="8">
         <v>2.7E-2</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G48" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C49,
@@ -63440,8 +63624,11 @@
       <c r="F49" s="8">
         <v>2.12E-2</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G49" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C50,
@@ -63466,8 +63653,11 @@
       <c r="F50" s="8">
         <v>8.0000000000000004E-4</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G50" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C51,
@@ -63492,8 +63682,11 @@
       <c r="F51" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G51" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C52,
@@ -63518,8 +63711,11 @@
       <c r="F52" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G52" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C53,
@@ -63544,8 +63740,11 @@
       <c r="F53" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G53" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <f>IFERROR(INDEX(char!$A:$A,
 MATCH(C54,
@@ -63570,8 +63769,11 @@
       <c r="F54" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G54" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
         <v>732</v>
       </c>
@@ -63585,8 +63787,11 @@
       <c r="D55" s="8">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G55" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B56" s="9"/>
     </row>
   </sheetData>
